--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-15T10:17:01.086Z</t>
+    <t>2026-09-16T07:06:02.589Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T07:06:02.589Z</t>
+    <t>2026-09-16T08:04:51.591Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T08:04:51.591Z</t>
+    <t>2026-09-16T08:50:03.832Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T08:50:03.832Z</t>
+    <t>2026-09-16T08:59:10.021Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T08:59:10.021Z</t>
+    <t>2026-09-16T09:11:49.700Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-promo","hero-banner","cards-plan","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
+    <t>["hero-promo","hero-banner","cards-plan","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T09:11:49.700Z</t>
+    <t>2026-09-16T09:25:50.632Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T09:25:50.632Z</t>
+    <t>2026-09-16T10:58:13.824Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T10:58:13.824Z</t>
+    <t>2026-09-16T11:11:05.496Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T11:11:05.496Z</t>
+    <t>2026-09-16T11:24:35.938Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T11:24:35.938Z</t>
+    <t>2026-09-16T12:10:06.891Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-promo","hero-banner","cards-plan","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
+    <t>["hero-promo","hero-banner","cards-plan","quicklinks-toggle","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T12:10:06.891Z</t>
+    <t>2026-09-16T12:21:17.144Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-promo","hero-banner","cards-plan","quicklinks-toggle","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
+    <t>["hero-promo","hero-banner","cards-plan","quicklinks-toggle","columns-product-recom","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T12:21:17.144Z</t>
+    <t>2026-09-16T13:01:39.346Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-promo","hero-banner","cards-plan","quicklinks-toggle","columns-product-recom","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","quote-callout","table-data","tabs-links","tabs-links","form","form"]</t>
+    <t>["hero-promo","hero-banner","cards-plan","quicklinks-toggle","columns-product-recom","cards-persona","cards-quicklink","cards-promo","cards-award","cards-stats","carousel-banner","cards-article","columns-panels","columns-panels","columns-panels","accordion-list","accordion-list","accordion-list","accordion-list","accordion-list","carousel-review","carousel-video","table-data","tabs-links","tabs-links","form","form"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-16T13:01:39.346Z</t>
+    <t>2026-09-16T17:02:34.798Z</t>
   </si>
   <si>
     <t>Life Insurance - Best Life Insurance Online in India 2026</t>
